--- a/CSLibraryHistoricalBranchesList.xlsx
+++ b/CSLibraryHistoricalBranchesList.xlsx
@@ -19,12 +19,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="69">
   <si>
     <t>CSLibrary</t>
-  </si>
-  <si>
-    <t>CSLibraryBT</t>
   </si>
   <si>
     <t>Model</t>
@@ -42,11 +39,6 @@
   </si>
   <si>
     <t>CSLibrary2024</t>
-  </si>
-  <si>
-    <t>TCP
-BLE 5
-BLE 4</t>
   </si>
   <si>
     <t>UI</t>
@@ -221,9 +213,6 @@
     <t>.Net Standard 2.1</t>
   </si>
   <si>
-    <t>.Net Standard 2.0</t>
-  </si>
-  <si>
     <t>CSLibraryBT-NETStandard21</t>
   </si>
   <si>
@@ -231,6 +220,32 @@
   </si>
   <si>
     <t>CSLibrary2024-NETStandard</t>
+  </si>
+  <si>
+    <t>BLE 5
+BLE 4</t>
+  </si>
+  <si>
+    <t>TCP</t>
+  </si>
+  <si>
+    <t>CSLibrary2024-NETStandard-TCP</t>
+  </si>
+  <si>
+    <t>CS203XL-C-Sharp-APP-for-iOS-ANDROID-UWP</t>
+  </si>
+  <si>
+    <t>CS203XL</t>
+  </si>
+  <si>
+    <t>CSLibrary2024TCP.NETSTD2.DLL</t>
+  </si>
+  <si>
+    <t>.Net Standard 2.0/2.1</t>
+  </si>
+  <si>
+    <t>CSLibraryBT
+(will phase out)</t>
   </si>
 </sst>
 </file>
@@ -261,7 +276,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="13">
+  <borders count="16">
     <border>
       <left/>
       <right/>
@@ -433,11 +448,48 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thick">
+        <color auto="1"/>
+      </left>
+      <right style="thick">
+        <color auto="1"/>
+      </right>
+      <top style="thick">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thick">
+        <color auto="1"/>
+      </left>
+      <right style="thick">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thick">
+        <color auto="1"/>
+      </left>
+      <right style="thick">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="thick">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -500,6 +552,24 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -829,7 +899,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A2:I15"/>
+  <dimension ref="A2:I16"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="17.140625" style="1" customWidth="1"/>
@@ -847,313 +917,340 @@
     <row r="2" spans="1:9" ht="15.75" thickBot="1"/>
     <row r="3" spans="1:9" ht="33.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="B3" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="D3" s="4" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="I3" s="8" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="33.75" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A4" s="21" t="s">
+      <c r="A4" s="24" t="s">
         <v>0</v>
       </c>
-      <c r="B4" s="19" t="s">
-        <v>36</v>
-      </c>
-      <c r="C4" s="19" t="s">
-        <v>5</v>
+      <c r="B4" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="C4" s="22" t="s">
+        <v>4</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E4" s="9" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="F4" s="9" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G4" s="9" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="H4" s="9" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="I4" s="14" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
     </row>
     <row r="5" spans="1:9" ht="33.75" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A5" s="21"/>
-      <c r="B5" s="20"/>
-      <c r="C5" s="20"/>
+      <c r="A5" s="24"/>
+      <c r="B5" s="23"/>
+      <c r="C5" s="23"/>
       <c r="D5" s="6" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E5" s="10" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F5" s="10" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G5" s="10" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="H5" s="10" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="I5" s="15" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="33.75" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A6" s="21"/>
-      <c r="B6" s="20"/>
-      <c r="C6" s="20"/>
+      <c r="A6" s="24"/>
+      <c r="B6" s="23"/>
+      <c r="C6" s="23"/>
       <c r="D6" s="6" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E6" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="F6" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="F6" s="10" t="s">
-        <v>13</v>
-      </c>
       <c r="G6" s="12" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="H6" s="10" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="I6" s="16" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="7" spans="1:9" ht="33.75" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A7" s="21"/>
-      <c r="B7" s="20"/>
-      <c r="C7" s="20"/>
+      <c r="A7" s="24"/>
+      <c r="B7" s="23"/>
+      <c r="C7" s="23"/>
       <c r="D7" s="7" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E7" s="11" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F7" s="11" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G7" s="13" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="H7" s="11" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="I7" s="17" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="8" spans="1:9" ht="33.75" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A8" s="20" t="s">
-        <v>1</v>
-      </c>
-      <c r="B8" s="19" t="s">
-        <v>37</v>
-      </c>
-      <c r="C8" s="20" t="s">
-        <v>4</v>
+      <c r="A8" s="22" t="s">
+        <v>68</v>
+      </c>
+      <c r="B8" s="22" t="s">
+        <v>35</v>
+      </c>
+      <c r="C8" s="23" t="s">
+        <v>3</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="E8" s="9" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F8" s="9" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="G8" s="9" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="H8" s="9" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="I8" s="14" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="9" spans="1:9" ht="33.75" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A9" s="20"/>
-      <c r="B9" s="20"/>
-      <c r="C9" s="20"/>
+      <c r="A9" s="23"/>
+      <c r="B9" s="23"/>
+      <c r="C9" s="23"/>
       <c r="D9" s="6" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E9" s="10" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="F9" s="10" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G9" s="10" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="H9" s="10" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="I9" s="15" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
     </row>
     <row r="10" spans="1:9" ht="33.75" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A10" s="20"/>
-      <c r="B10" s="20"/>
-      <c r="C10" s="20"/>
+      <c r="A10" s="23"/>
+      <c r="B10" s="23"/>
+      <c r="C10" s="23"/>
       <c r="D10" s="7" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="E10" s="11" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F10" s="11" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G10" s="11" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="H10" s="11" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="I10" s="18" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="11" spans="1:9" ht="33.75" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A11" s="20" t="s">
-        <v>6</v>
-      </c>
-      <c r="B11" s="19" t="s">
-        <v>38</v>
-      </c>
-      <c r="C11" s="19" t="s">
-        <v>7</v>
+      <c r="A11" s="25" t="s">
+        <v>5</v>
+      </c>
+      <c r="B11" s="22" t="s">
+        <v>36</v>
+      </c>
+      <c r="C11" s="22" t="s">
+        <v>61</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E11" s="9" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="F11" s="9" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="G11" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="H11" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="I11" s="14" t="s">
         <v>56</v>
-      </c>
-      <c r="H11" s="9" t="s">
-        <v>54</v>
-      </c>
-      <c r="I11" s="14" t="s">
-        <v>58</v>
       </c>
     </row>
     <row r="12" spans="1:9" ht="33.75" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A12" s="20"/>
-      <c r="B12" s="20"/>
-      <c r="C12" s="20"/>
+      <c r="A12" s="26"/>
+      <c r="B12" s="23"/>
+      <c r="C12" s="23"/>
       <c r="D12" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="E12" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="F12" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="G12" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="H12" s="10" t="s">
         <v>53</v>
       </c>
-      <c r="E12" s="10" t="s">
-        <v>43</v>
-      </c>
-      <c r="F12" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="G12" s="10" t="s">
-        <v>57</v>
-      </c>
-      <c r="H12" s="10" t="s">
-        <v>55</v>
-      </c>
       <c r="I12" s="15" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
     </row>
     <row r="13" spans="1:9" ht="33.75" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A13" s="20"/>
-      <c r="B13" s="20"/>
-      <c r="C13" s="20"/>
+      <c r="A13" s="26"/>
+      <c r="B13" s="23"/>
+      <c r="C13" s="23"/>
       <c r="D13" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="E13" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="F13" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="G13" s="10" t="s">
         <v>60</v>
       </c>
-      <c r="E13" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="F13" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="G13" s="10" t="s">
-        <v>63</v>
-      </c>
       <c r="H13" s="10" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="I13" s="15" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
     </row>
     <row r="14" spans="1:9" ht="33.75" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A14" s="20"/>
-      <c r="B14" s="20"/>
-      <c r="C14" s="20"/>
+      <c r="A14" s="26"/>
+      <c r="B14" s="23"/>
+      <c r="C14" s="23"/>
       <c r="D14" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="E14" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="F14" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="G14" s="11" t="s">
         <v>33</v>
       </c>
-      <c r="E14" s="11" t="s">
-        <v>11</v>
-      </c>
-      <c r="F14" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="G14" s="11" t="s">
-        <v>35</v>
-      </c>
       <c r="H14" s="11" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="I14" s="17" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" ht="33.75" customHeight="1" thickTop="1" thickBot="1">
+      <c r="A15" s="27"/>
+      <c r="B15" s="19" t="s">
+        <v>65</v>
+      </c>
+      <c r="C15" s="21" t="s">
         <v>62</v>
       </c>
+      <c r="D15" s="21" t="s">
+        <v>67</v>
+      </c>
+      <c r="E15" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="F15" s="20" t="s">
+        <v>22</v>
+      </c>
+      <c r="G15" s="20" t="s">
+        <v>63</v>
+      </c>
+      <c r="H15" s="20" t="s">
+        <v>66</v>
+      </c>
+      <c r="I15" s="8" t="s">
+        <v>64</v>
+      </c>
     </row>
-    <row r="15" spans="1:9" ht="15.75" thickTop="1"/>
+    <row r="16" spans="1:9" ht="15.75" thickTop="1"/>
   </sheetData>
   <mergeCells count="9">
     <mergeCell ref="C11:C14"/>
     <mergeCell ref="B11:B14"/>
-    <mergeCell ref="A11:A14"/>
     <mergeCell ref="C4:C7"/>
     <mergeCell ref="B4:B7"/>
     <mergeCell ref="A4:A7"/>
     <mergeCell ref="C8:C10"/>
     <mergeCell ref="B8:B10"/>
     <mergeCell ref="A8:A10"/>
+    <mergeCell ref="A11:A15"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
